--- a/resources/路网表头映射关系.xlsx
+++ b/resources/路网表头映射关系.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <t>中文表头</t>
   </si>
   <si>
-    <t>对应该列数据处理方式</t>
+    <t>备注</t>
   </si>
   <si>
     <t>起点</t>
